--- a/dashboard-ui/src/components/Research/variables/Variable Definitions RQ134_PH2_Can_UK2026.xlsx
+++ b/dashboard-ui/src/components/Research/variables/Variable Definitions RQ134_PH2_Can_UK2026.xlsx
@@ -209,7 +209,7 @@
     <t>1 - 19</t>
   </si>
   <si>
-    <t>AF-SS;  PS-Bi; PS-Tri; AF-Bi; AF-Tri</t>
+    <t>AF-SS, PS, MF, AF, MF-SS</t>
   </si>
   <si>
     <t xml:space="preserve">(E.g., Mistral, DeepSeek, Llama) </t>
